--- a/Inp-Out/usn_list.xlsx
+++ b/Inp-Out/usn_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\india\Desktop\VTU_results\Inp-Out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953E706C-43C0-4116-B0F2-459065929177}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D61F2AAB-0C71-4319-9835-2CD2FBE2D9BD}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D3C98C4-02F0-4FB4-9D88-793BC642E170}"/>
   </bookViews>
@@ -35,19 +35,19 @@
     <t>USN</t>
   </si>
   <si>
-    <t>1AM22AI001</t>
-  </si>
-  <si>
-    <t>1AM22AI002</t>
-  </si>
-  <si>
-    <t>1AM22AI003</t>
-  </si>
-  <si>
-    <t>1AM22AI004</t>
-  </si>
-  <si>
-    <t>1AM22AI005</t>
+    <t>1XX22XX001</t>
+  </si>
+  <si>
+    <t>1XX22XX002</t>
+  </si>
+  <si>
+    <t>1XX22XX003</t>
+  </si>
+  <si>
+    <t>1XX22XX004</t>
+  </si>
+  <si>
+    <t>1XX22XX005</t>
   </si>
 </sst>
 </file>

--- a/Inp-Out/usn_list.xlsx
+++ b/Inp-Out/usn_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\india\Desktop\VTU_results\Inp-Out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D61F2AAB-0C71-4319-9835-2CD2FBE2D9BD}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{629DD3D1-669F-429B-85DB-73FC4C4409C8}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D3C98C4-02F0-4FB4-9D88-793BC642E170}"/>
   </bookViews>
